--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -30827,12 +30827,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -30857,12 +30857,12 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N154" t="n">
@@ -30871,6 +30871,9 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -30881,12 +30884,12 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>SER_KR_NIPAH</t>
+          <t>SER_JP_NIPAH_WEEKLY</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -30906,7 +30909,7 @@
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>SER_KR_NIPAH</t>
+          <t>SER_JP_NIPAH_WEEKLY</t>
         </is>
       </c>
       <c r="AT154" t="n">
@@ -30919,42 +30922,42 @@
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30986,12 +30989,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -31016,12 +31019,12 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N155" t="n">
@@ -31030,24 +31033,27 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>SER_KR_NIPAH</t>
+          <t>SER_JP_NIPAH_WEEKLY</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>SER_KR_NIPAH</t>
+          <t>SER_JP_NIPAH_WEEKLY</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>@니파바이러스감염증</t>
+          <t>Nipah virus infection</t>
         </is>
       </c>
       <c r="Y155" t="inlineStr">
@@ -31062,7 +31068,7 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
@@ -31072,7 +31078,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD155" t="inlineStr">
@@ -31112,7 +31118,7 @@
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>Korea KDCA Nipah virus infection notifications.</t>
+          <t>Japan NIID Nipah virus infection notifications, distinct from Hendra virus infection.</t>
         </is>
       </c>
       <c r="AM155" t="inlineStr">
@@ -31140,7 +31146,7 @@
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>SER_KR_NIPAH</t>
+          <t>SER_JP_NIPAH_WEEKLY</t>
         </is>
       </c>
       <c r="AT155" t="n">
@@ -31153,40 +31159,433 @@
       </c>
       <c r="AV155" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW155" t="inlineStr">
+      <c r="AW156" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX155" t="inlineStr">
+      <c r="AX156" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY155" t="inlineStr">
+      <c r="AY156" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ155" t="inlineStr">
+      <c r="AZ156" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA155" t="inlineStr">
+      <c r="BA156" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB155" t="inlineStr">
+      <c r="BB156" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC155" t="inlineStr">
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>@니파바이러스감염증</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Korea KDCA Nipah virus infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -31308,7 +31707,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -31318,7 +31717,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -31338,7 +31737,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -31226,12 +31226,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -31256,12 +31256,12 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N156" t="n">
@@ -31270,6 +31270,9 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -31278,14 +31281,9 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>SER_KR_NIPAH</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -31295,7 +31293,7 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
@@ -31305,55 +31303,55 @@
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>SER_KR_NIPAH</t>
+          <t>SER_SG_CDA_NIPAH; SER_SG_HIST_NIPAH</t>
         </is>
       </c>
       <c r="AT156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -31385,12 +31383,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -31415,12 +31413,12 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N157" t="n">
@@ -31429,24 +31427,27 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>SER_KR_NIPAH</t>
+          <t>SER_SG_CDA_NIPAH</t>
         </is>
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>SER_KR_NIPAH</t>
+          <t>SER_SG_CDA_NIPAH</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>@니파바이러스감염증</t>
+          <t>Nipah</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
@@ -31456,12 +31457,12 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
@@ -31471,7 +31472,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD157" t="inlineStr">
@@ -31486,7 +31487,7 @@
       </c>
       <c r="AF157" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG157" t="inlineStr">
@@ -31506,12 +31507,12 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>Korea KDCA Nipah virus infection notifications.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
@@ -31529,63 +31530,456 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_NIPAH; SER_SG_HIST_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ157" t="inlineStr">
+      <c r="AQ158" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS157" t="inlineStr">
+      <c r="AS158" t="inlineStr">
         <is>
           <t>SER_KR_NIPAH</t>
         </is>
       </c>
-      <c r="AT157" t="n">
+      <c r="AT158" t="n">
         <v>1</v>
       </c>
-      <c r="AU157" t="inlineStr">
+      <c r="AU158" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV157" t="inlineStr">
+      <c r="AV158" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW157" t="inlineStr">
+      <c r="AW158" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX157" t="inlineStr">
+      <c r="AX158" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY157" t="inlineStr">
+      <c r="AY158" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ157" t="inlineStr">
+      <c r="AZ158" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA157" t="inlineStr">
+      <c r="BA158" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB157" t="inlineStr">
+      <c r="BB158" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC157" t="inlineStr">
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>@니파바이러스감염증</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Korea KDCA Nipah virus infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -31707,7 +32101,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -31717,7 +32111,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
@@ -31737,7 +32131,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -31985,6 +31985,405 @@
         </is>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Japan NIID Nipah virus infection notifications, distinct from Hendra virus infection.</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN161" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -32018,7 +32417,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -32101,7 +32500,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -32111,7 +32510,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -32131,7 +32530,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -32384,6 +32384,400 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_NIPAH; SER_SG_HIST_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_NIPAH</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_NIPAH</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>Nipah</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN163" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_NIPAH; SER_SG_HIST_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -32500,7 +32894,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -32510,7 +32904,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -32530,7 +32924,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11702,7 +11702,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16453,7 +16453,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17246,7 +17246,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18039,7 +18039,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19625,7 +19625,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20412,7 +20412,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20811,7 +20811,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21604,7 +21604,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23190,7 +23190,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24376,7 +24376,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25169,7 +25169,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25962,7 +25962,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26755,7 +26755,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27941,7 +27941,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29527,7 +29527,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30320,7 +30320,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31113,7 +31113,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31900,7 +31900,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32299,7 +32299,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32773,6 +32773,799 @@
         </is>
       </c>
       <c r="BC163" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Japan NIID Nipah virus infection notifications, distinct from Hendra virus infection.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_NIPAH; SER_SG_HIST_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_NIPAH</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_NIPAH</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Nipah</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_NIPAH; SER_SG_HIST_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -32811,7 +33604,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -32894,7 +33687,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -32904,7 +33697,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -32924,7 +33717,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -33571,6 +33571,1192 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Japan NIID Nipah virus infection notifications, distinct from Hendra virus infection.</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN169" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_NIPAH; SER_SG_HIST_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_NIPAH</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_NIPAH</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>Nipah</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN171" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_NIPAH; SER_SG_HIST_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>@니파바이러스감염증</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Korea KDCA Nipah virus infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN173" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33604,7 +34790,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -33687,7 +34873,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -33697,7 +34883,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -33717,7 +34903,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -34392,12 +34392,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -34422,12 +34422,12 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N172" t="n">
@@ -34436,6 +34436,9 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -34446,12 +34449,12 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>SER_KR_NIPAH</t>
+          <t>SER_JP_NIPAH_WEEKLY</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -34471,7 +34474,7 @@
       </c>
       <c r="AS172" t="inlineStr">
         <is>
-          <t>SER_KR_NIPAH</t>
+          <t>SER_JP_NIPAH_WEEKLY</t>
         </is>
       </c>
       <c r="AT172" t="n">
@@ -34484,42 +34487,42 @@
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34551,12 +34554,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -34581,12 +34584,12 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N173" t="n">
@@ -34595,24 +34598,27 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>SER_KR_NIPAH</t>
+          <t>SER_JP_NIPAH_WEEKLY</t>
         </is>
       </c>
       <c r="V173" t="inlineStr">
         <is>
-          <t>SER_KR_NIPAH</t>
+          <t>SER_JP_NIPAH_WEEKLY</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>@니파바이러스감염증</t>
+          <t>Nipah virus infection</t>
         </is>
       </c>
       <c r="Y173" t="inlineStr">
@@ -34627,7 +34633,7 @@
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr">
@@ -34637,7 +34643,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr">
@@ -34677,7 +34683,7 @@
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Korea KDCA Nipah virus infection notifications.</t>
+          <t>Japan NIID Nipah virus infection notifications, distinct from Hendra virus infection.</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
@@ -34705,7 +34711,7 @@
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>SER_KR_NIPAH</t>
+          <t>SER_JP_NIPAH_WEEKLY</t>
         </is>
       </c>
       <c r="AT173" t="n">
@@ -34718,40 +34724,433 @@
       </c>
       <c r="AV173" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV174" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW173" t="inlineStr">
+      <c r="AW174" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX173" t="inlineStr">
+      <c r="AX174" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY173" t="inlineStr">
+      <c r="AY174" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ173" t="inlineStr">
+      <c r="AZ174" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA173" t="inlineStr">
+      <c r="BA174" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB173" t="inlineStr">
+      <c r="BB174" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC173" t="inlineStr">
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>@니파바이러스감염증</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>Korea KDCA Nipah virus infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN175" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA175" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC175" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -34873,7 +35272,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -34883,7 +35282,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -34903,7 +35302,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -34791,12 +34791,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -34821,12 +34821,12 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N174" t="n">
@@ -34835,6 +34835,9 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -34843,14 +34846,9 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t>SER_KR_NIPAH</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -34860,7 +34858,7 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
@@ -34870,55 +34868,55 @@
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>SER_KR_NIPAH</t>
+          <t>SER_SG_CDA_NIPAH; SER_SG_HIST_NIPAH</t>
         </is>
       </c>
       <c r="AT174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34950,12 +34948,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -34980,12 +34978,12 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N175" t="n">
@@ -34994,24 +34992,27 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
       <c r="U175" t="inlineStr">
         <is>
-          <t>SER_KR_NIPAH</t>
+          <t>SER_SG_CDA_NIPAH</t>
         </is>
       </c>
       <c r="V175" t="inlineStr">
         <is>
-          <t>SER_KR_NIPAH</t>
+          <t>SER_SG_CDA_NIPAH</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>@니파바이러스감염증</t>
+          <t>Nipah</t>
         </is>
       </c>
       <c r="Y175" t="inlineStr">
@@ -35021,12 +35022,12 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr">
@@ -35036,7 +35037,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD175" t="inlineStr">
@@ -35051,7 +35052,7 @@
       </c>
       <c r="AF175" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG175" t="inlineStr">
@@ -35071,12 +35072,12 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>Korea KDCA Nipah virus infection notifications.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM175" t="inlineStr">
@@ -35094,63 +35095,456 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_NIPAH; SER_SG_HIST_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA175" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC175" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="R176" t="n">
+        <v>0</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP176" t="inlineStr">
+        <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ175" t="inlineStr">
+      <c r="AQ176" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS175" t="inlineStr">
+      <c r="AS176" t="inlineStr">
         <is>
           <t>SER_KR_NIPAH</t>
         </is>
       </c>
-      <c r="AT175" t="n">
+      <c r="AT176" t="n">
         <v>1</v>
       </c>
-      <c r="AU175" t="inlineStr">
+      <c r="AU176" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV175" t="inlineStr">
+      <c r="AV176" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW175" t="inlineStr">
+      <c r="AW176" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX175" t="inlineStr">
+      <c r="AX176" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY175" t="inlineStr">
+      <c r="AY176" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ175" t="inlineStr">
+      <c r="AZ176" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA175" t="inlineStr">
+      <c r="BA176" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB175" t="inlineStr">
+      <c r="BB176" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC175" t="inlineStr">
+      <c r="BC176" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>@니파바이러스감염증</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>Korea KDCA Nipah virus infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN177" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>SER_KR_NIPAH</t>
+        </is>
+      </c>
+      <c r="AT177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV177" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA177" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB177" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC177" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -35272,7 +35666,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -35282,7 +35676,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -35302,7 +35696,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d175/2026-2029.xlsx
+++ b/diseases/d175/2026-2029.xlsx
@@ -35550,6 +35550,405 @@
         </is>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB178" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC178" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>nipah-virus-infection</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>D175</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>立百病毒感染</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>Nipah virus infection</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Japan NIID Nipah virus infection notifications, distinct from Hendra virus infection.</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN179" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP179" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>SER_JP_NIPAH_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV179" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA179" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB179" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC179" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35583,7 +35982,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -35666,7 +36065,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -35676,7 +36075,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -35696,7 +36095,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13">
